--- a/AI_QRS_Unit_Test_Plan.xlsx
+++ b/AI_QRS_Unit_Test_Plan.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -46,8 +46,12 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +72,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6A000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -135,6 +149,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1135,6 +1152,1715 @@
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>--- Milestone 3 Test Results ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Date Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>M3-T01</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Clear factual query not flagged ambiguous</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=False</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=False</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>M3-T02</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Pure pronoun query ambiguous without history</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=True</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=True</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>M3-T03</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Vague-noun query requires clarification</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=True</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=True</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>M3-T04</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Open-ended follow-up always ambiguous</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=True</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=True</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>M3-T05</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Targeted question mentions vague noun</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>noun in question</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>noun in question</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>M3-T06</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Original query preserved in result</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>original_query==q</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>original_query==q</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>M3-T07</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationState created with pending=True</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>state.pending=True</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>state.pending=True</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>M3-T08</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>refine_query combines original + clarification</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>terms in refined</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>terms in refined</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>M3-T09</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>refine_query handles pronoun substitution</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>response in refined</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>response in refined</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>M3-T10</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>ClarificationAgent</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Rich key terms (&gt;=3) not ambiguous</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=False</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>is_ambiguous=False</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>M3-T11</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Session memory created empty</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>history=[], topic=None</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>history=[], topic=None</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>M3-T12</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Previous user query stored</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>history len=1</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>history len=1</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>M3-T13</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Previous assistant answer stored</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>history len=2</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>history len=2</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>M3-T14</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Pronoun resolution uses last entities</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>entity in resolved</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>entity in resolved</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>M3-T15</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Topic continuation detected on term overlap</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>is_continuation=True</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>is_continuation=True</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>M3-T16</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Context switch detected on no term overlap</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>is_continuation=False</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>is_continuation=False</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>M3-T17</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Switched topic returns empty context</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>context==[]</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>context==[]</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>M3-T18</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>History bounded to max_history</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>len(history)==10</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>len(history)==10</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>M3-T19</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Missing context returns original query</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>resolved==original</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>resolved==original</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>M3-T20</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Session isolation - agents dont share state</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>memory2.history==[]</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>memory2.history==[]</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>M3-T21</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Pending clarification stored and consumed</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>consumed.original==q</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>consumed.original==q</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>M3-T22</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>consume_clarification returns None when empty</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>result==None</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>result==None</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>M3-T23</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>update_topic stores source docs</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>doc in last_source_docs</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>doc in last_source_docs</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>M3-T24</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>ConversationMemoryAgent</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>clear() resets all state</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>history=[], topic=None</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>history=[], topic=None</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>M3-T25</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Sources contain text field</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>text in sources[0]</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>text in sources[0]</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>M3-T26</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Sources contain page_number</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>page_number==5</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>page_number==5</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>M3-T27</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Sources contain chunk_id</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>chunk_id==c-1</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>chunk_id==c-1</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>M3-T28</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Sources contain similarity_score</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>score within 0.0001</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>score within 0.0001</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>M3-T29</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Sources contain citation labels [1],[2]</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>citation==[1]</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>citation==[1]</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>M3-T30</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Sources contain document_name field</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>document_name==file</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>document_name==file</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>M3-T31</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Confidence from retrieval mean</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>confidence&gt;0</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>confidence&gt;0</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>M3-T32</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Evidence matches retrieval output</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>text in sources</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>text in sources</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>M3-T33</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Low confidence when no results</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>confidence==0.0</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>confidence==0.0</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>M3-T34</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Empty sources when no chunks</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>sources==[]</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>sources==[]</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>M3-T35</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>TransparencyPanel</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Chunk text truncated at 600 chars</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>len(text)&lt;=600</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>len(text)&lt;=600</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>M3-T36</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Clear factual query returns grounded answer</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>clarification_needed=False</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>clarification_needed=False</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>M3-T37</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Ambiguous query returns clarification question</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>clarification_needed=True</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>clarification_needed=True</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>M3-T38</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Full clarification cycle resolved</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>result2.clarification_needed=False</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>result2.clarification_needed=False</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>M3-T39</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Multi-turn pronoun resolution</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>result2 is OrchestratorResult</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>result2 is OrchestratorResult</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>M3-T40</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Knowledge gap returns confidence=0</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>confidence==0.0</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>confidence==0.0</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>M3-T41</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Refined query set after clarification</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>refined_query!=empty</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>refined_query!=empty</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>M3-T42</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Topic switch - old topic not contaminated</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>context_before_switch==[]</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>context_before_switch==[]</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>M3-T43</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>All M3.4 fields present in sources</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>all fields present</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>all fields present</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>M3-T44</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>used_memory_context flag on topic continuation</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>used_memory_context=True</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>used_memory_context=True</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>M3-T45</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Orchestrator E2E</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Greeting bypasses RAG pipeline</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>retrieval_count==0</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>retrieval_count==0</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
